--- a/artfynd/A 2068-2024 artfynd.xlsx
+++ b/artfynd/A 2068-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2068-2024 artfynd.xlsx
+++ b/artfynd/A 2068-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2895,6 +2895,1031 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118135198</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>588614</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7026717</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118135385</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>588670</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7027039</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118135227</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95133</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>588618</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7026719</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118135199</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>588621</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7026722</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118135226</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95133</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>588572</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7026778</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118135197</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>588614</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7026721</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118135210</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>588618</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7026719</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118135153</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>588567</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7026775</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118135225</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79598</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>588621</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7026722</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118135154</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90501</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Salsjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>588572</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7026778</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
